--- a/teachers.xlsx
+++ b/teachers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\house-point-system-webapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C42F94-3E47-4F44-9062-381086E56493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2E0499-D06D-4893-8BF7-F27F4D4CF46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{988623B5-A906-4EE0-ABB2-2E4498BF3802}"/>
   </bookViews>
@@ -171,15 +171,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -187,12 +193,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,10 +623,10 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -618,10 +637,10 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -631,11 +650,11 @@
       <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -645,11 +664,11 @@
       <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -660,10 +679,10 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -674,10 +693,10 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -687,11 +706,11 @@
       <c r="A8" t="s">
         <v>33</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -701,11 +720,11 @@
       <c r="A9" t="s">
         <v>34</v>
       </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D9">
         <v>4</v>
